--- a/商品一覧.xlsx
+++ b/商品一覧.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8b7225abb1e4bba2/Desktop/ECサイト/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{9CABAA21-02B6-4033-8C12-46D8AFD5FBAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4CF117F-1A3B-46F1-9907-9FB5B4030BDC}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="8_{9CABAA21-02B6-4033-8C12-46D8AFD5FBAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7053932B-3E88-4CFB-A400-3E058653113B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B0671FC1-4AEA-446C-9F92-E11BD877F195}"/>
+    <workbookView xWindow="1100" yWindow="1100" windowWidth="14400" windowHeight="7270" xr2:uid="{B0671FC1-4AEA-446C-9F92-E11BD877F195}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="57">
   <si>
     <t>商品ID</t>
     <rPh sb="0" eb="2">
@@ -180,6 +180,230 @@
     <rPh sb="0" eb="2">
       <t>コウカイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品2</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品3</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品4</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品5</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品6</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品7</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>肉球クリーム</t>
+    <rPh sb="0" eb="2">
+      <t>ニクキュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LION</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>肉球つやつや</t>
+    <rPh sb="0" eb="2">
+      <t>ニクキュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>つやつやになります</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペースト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>無理しないように</t>
+    <rPh sb="0" eb="2">
+      <t>ムリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>肉球潤いマン</t>
+    <rPh sb="0" eb="2">
+      <t>ニクキュウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ウルオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アニフル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高すぎ！</t>
+    <rPh sb="0" eb="1">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>液体</t>
+    <rPh sb="0" eb="2">
+      <t>エキタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シャンプー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>犬用シャンプー</t>
+    <rPh sb="0" eb="2">
+      <t>イヌヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ただのシャンプーです</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被毛が良くなる！</t>
+    <rPh sb="0" eb="2">
+      <t>ヒモウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>泡</t>
+    <rPh sb="0" eb="1">
+      <t>アワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ORIGINAL歯磨き</t>
+    <rPh sb="8" eb="10">
+      <t>ハミガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オリジナルの歯磨きです</t>
+    <rPh sb="6" eb="8">
+      <t>ハミガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>口臭対策にすごくいい</t>
+    <rPh sb="0" eb="4">
+      <t>コウシュウタイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モアモット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>売れ筋ナンバーワン！</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>スジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ホワイトニングにいいよ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジェル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>口に入れて</t>
+    <rPh sb="0" eb="1">
+      <t>クチ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>火に近づけない</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>チカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スプレー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被毛がつやつやスプレー</t>
+    <rPh sb="0" eb="2">
+      <t>ヒモウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5カ月使うとつやつやに</t>
+    <rPh sb="2" eb="4">
+      <t>ゲツツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>おすすめ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -187,7 +411,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,6 +433,14 @@
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -236,12 +468,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -254,8 +489,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -269,6 +511,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -588,14 +834,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A7AB50-F0EE-4CCC-8BCD-07850E8E7861}">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="10.4140625" style="3" customWidth="1"/>
-    <col min="2" max="13" width="10.4140625" customWidth="1"/>
+    <col min="2" max="4" width="10.4140625" customWidth="1"/>
+    <col min="5" max="5" width="10.4140625" style="5" customWidth="1"/>
+    <col min="6" max="13" width="10.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -608,7 +856,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -635,8 +883,11 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -649,7 +900,7 @@
       <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="5">
         <v>2640</v>
       </c>
       <c r="F2" t="s">
@@ -669,6 +920,207 @@
       </c>
       <c r="M2" t="s">
         <v>21</v>
+      </c>
+      <c r="N2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="5">
+        <v>3000</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="5">
+        <v>30000</v>
+      </c>
+      <c r="F4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="5">
+        <v>100020</v>
+      </c>
+      <c r="F5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="5">
+        <v>100</v>
+      </c>
+      <c r="F6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" t="s">
+        <v>49</v>
+      </c>
+      <c r="J6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="5">
+        <v>12044</v>
+      </c>
+      <c r="F7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="5">
+        <v>4031</v>
+      </c>
+      <c r="J8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
